--- a/data/Quality control/ghg_comparison.xlsx
+++ b/data/Quality control/ghg_comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Quality control/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_23F921EDEF3B4DDA757F8C432F70DF2C7452AFE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CE60151-BC9A-4BE6-A65E-439BC8BB0724}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_23F921EDEF3B4DDA757F8C432F70DF2C7452AFE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF989C5B-BEAC-47EE-A866-D16A7344A5B6}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -18,16 +18,29 @@
     <sheet name="ghg_flows" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ghg_flows!$A$1:$N$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">nrj_flows!$A$1:$Q$138</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="451">
   <si>
     <t>tCO2eq_estimated</t>
   </si>
@@ -1374,13 +1387,19 @@
   </si>
   <si>
     <t>GRP-de097f20</t>
+  </si>
+  <si>
+    <t>Energy mix is derived from the company overall mix. GHG from stats</t>
+  </si>
+  <si>
+    <t>No explanation (Macassa from Agnico)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1392,6 +1411,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1417,7 +1444,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1440,26 +1467,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1473,6 +1517,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1772,6 +1820,7 @@
     <col min="5" max="5" width="11.81640625" customWidth="1"/>
     <col min="6" max="6" width="14.26953125" customWidth="1"/>
     <col min="7" max="7" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="59.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1796,6 +1845,9 @@
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H1" s="7" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
@@ -1815,6 +1867,9 @@
       <c r="G2" s="4">
         <v>8.92495441271179E-2</v>
       </c>
+      <c r="H2" t="s">
+        <v>449</v>
+      </c>
       <c r="J2" s="4" t="s">
         <v>39</v>
       </c>
@@ -2087,6 +2142,9 @@
       <c r="G16" s="4">
         <v>0.27707531318069673</v>
       </c>
+      <c r="H16" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
@@ -2412,7 +2470,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2495,7 +2553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -2545,7 +2603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -2595,7 +2653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -4396,7 +4454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -4443,7 +4501,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -4490,7 +4548,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>143</v>
       </c>
@@ -4537,7 +4595,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -4584,7 +4642,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -8986,7 +9044,7 @@
   <autoFilter ref="A1:Q138" xr:uid="{75298D18-3804-4E91-8F78-83C319CABDF1}">
     <filterColumn colId="7">
       <filters>
-        <filter val="BC-MAIN-599152a0"/>
+        <filter val="ON-MAIN-1f126a43"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8996,7 +9054,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E536B50-14E2-4386-94C9-9FE4EFA7586F}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9060,7 +9117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>287</v>
       </c>
@@ -9098,7 +9155,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>296</v>
       </c>
@@ -9136,7 +9193,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>299</v>
       </c>
@@ -9174,7 +9231,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>302</v>
       </c>
@@ -9212,7 +9269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>303</v>
       </c>
@@ -9250,7 +9307,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>306</v>
       </c>
@@ -9288,7 +9345,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>309</v>
       </c>
@@ -9326,7 +9383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>310</v>
       </c>
@@ -9364,7 +9421,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>313</v>
       </c>
@@ -9402,7 +9459,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>315</v>
       </c>
@@ -9440,7 +9497,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>318</v>
       </c>
@@ -9478,7 +9535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>319</v>
       </c>
@@ -9516,7 +9573,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>320</v>
       </c>
@@ -9554,7 +9611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>321</v>
       </c>
@@ -9592,7 +9649,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>324</v>
       </c>
@@ -9630,7 +9687,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>325</v>
       </c>
@@ -9668,7 +9725,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>328</v>
       </c>
@@ -9706,7 +9763,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>331</v>
       </c>
@@ -9744,7 +9801,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>333</v>
       </c>
@@ -9782,7 +9839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>334</v>
       </c>
@@ -9820,7 +9877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>335</v>
       </c>
@@ -9858,7 +9915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>336</v>
       </c>
@@ -9896,7 +9953,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>339</v>
       </c>
@@ -9934,7 +9991,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>342</v>
       </c>
@@ -9972,7 +10029,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>343</v>
       </c>
@@ -10010,7 +10067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>344</v>
       </c>
@@ -10048,7 +10105,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>347</v>
       </c>
@@ -10086,7 +10143,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>349</v>
       </c>
@@ -10124,7 +10181,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>350</v>
       </c>
@@ -10162,7 +10219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>351</v>
       </c>
@@ -10200,7 +10257,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>354</v>
       </c>
@@ -10238,7 +10295,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>357</v>
       </c>
@@ -10276,7 +10333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>358</v>
       </c>
@@ -10314,7 +10371,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>361</v>
       </c>
@@ -10352,7 +10409,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>364</v>
       </c>
@@ -10390,7 +10447,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>365</v>
       </c>
@@ -10428,7 +10485,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>366</v>
       </c>
@@ -10497,14 +10554,14 @@
       <c r="L39" t="s">
         <v>61</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="8" t="s">
         <v>295</v>
       </c>
       <c r="N39" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>368</v>
       </c>
@@ -10542,7 +10599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>369</v>
       </c>
@@ -10580,7 +10637,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>370</v>
       </c>
@@ -10618,7 +10675,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>373</v>
       </c>
@@ -10656,7 +10713,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -10694,7 +10751,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>377</v>
       </c>
@@ -10732,7 +10789,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>380</v>
       </c>
@@ -10770,7 +10827,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>383</v>
       </c>
@@ -10808,7 +10865,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>386</v>
       </c>
@@ -10846,7 +10903,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>389</v>
       </c>
@@ -10884,7 +10941,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>392</v>
       </c>
@@ -10922,7 +10979,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>395</v>
       </c>
@@ -10960,7 +11017,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>398</v>
       </c>
@@ -10998,7 +11055,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>401</v>
       </c>
@@ -11036,7 +11093,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>403</v>
       </c>
@@ -11074,7 +11131,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>405</v>
       </c>
@@ -11112,7 +11169,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>407</v>
       </c>
@@ -11150,7 +11207,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>410</v>
       </c>
@@ -11188,7 +11245,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>413</v>
       </c>
@@ -11226,7 +11283,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>416</v>
       </c>
@@ -11264,7 +11321,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>418</v>
       </c>
@@ -11302,7 +11359,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>420</v>
       </c>
@@ -11340,7 +11397,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>422</v>
       </c>
@@ -11378,7 +11435,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>425</v>
       </c>
@@ -11416,7 +11473,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>427</v>
       </c>
@@ -11454,7 +11511,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>428</v>
       </c>
@@ -11492,7 +11549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>430</v>
       </c>
@@ -11530,7 +11587,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>431</v>
       </c>
@@ -11568,7 +11625,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>432</v>
       </c>
@@ -11606,7 +11663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>434</v>
       </c>
@@ -11644,7 +11701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B70">
         <v>2023</v>
       </c>
@@ -11682,7 +11739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B71">
         <v>2023</v>
       </c>
@@ -11717,7 +11774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B72">
         <v>2023</v>
       </c>
@@ -11755,7 +11812,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B73">
         <v>2023</v>
       </c>
@@ -11793,7 +11850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B74">
         <v>2023</v>
       </c>
@@ -11828,7 +11885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B75">
         <v>2023</v>
       </c>
@@ -11866,7 +11923,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B76">
         <v>2023</v>
       </c>
@@ -11901,7 +11958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B77">
         <v>2023</v>
       </c>
@@ -11939,7 +11996,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B78">
         <v>2023</v>
       </c>
@@ -11977,7 +12034,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B79">
         <v>2023</v>
       </c>
@@ -12015,7 +12072,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B80">
         <v>2023</v>
       </c>
@@ -12053,7 +12110,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="81" spans="2:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B81">
         <v>2023</v>
       </c>
@@ -12091,7 +12148,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="82" spans="2:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B82">
         <v>2023</v>
       </c>
@@ -12126,7 +12183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="2:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B83">
         <v>2023</v>
       </c>
@@ -12164,7 +12221,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="84" spans="2:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B84">
         <v>2023</v>
       </c>
@@ -12202,7 +12259,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="85" spans="2:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B85">
         <v>2023</v>
       </c>
@@ -12241,13 +12298,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N85" xr:uid="{9E536B50-14E2-4386-94C9-9FE4EFA7586F}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="BC-MAIN-599152a0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N85" xr:uid="{9E536B50-14E2-4386-94C9-9FE4EFA7586F}"/>
+  <hyperlinks>
+    <hyperlink ref="M39" r:id="rId1" xr:uid="{2268066F-0387-4081-A3D5-A34662CE6FE4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Quality control/ghg_comparison.xlsx
+++ b/data/Quality control/ghg_comparison.xlsx
@@ -575,16 +575,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>23612.49945893959</v>
+        <v>23612.4993404836</v>
       </c>
       <c r="C6">
         <v>15908.3</v>
       </c>
       <c r="D6">
-        <v>7704.199458939594</v>
+        <v>7704.199340483596</v>
       </c>
       <c r="E6">
-        <v>1.484288042024578</v>
+        <v>1.484288034578402</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -592,16 +592,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>74891.21346448729</v>
+        <v>74891.21331786228</v>
       </c>
       <c r="C7">
         <v>72492</v>
       </c>
       <c r="D7">
-        <v>2399.213464487286</v>
+        <v>2399.213317862275</v>
       </c>
       <c r="E7">
-        <v>1.033096251510336</v>
+        <v>1.033096249487699</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -609,16 +609,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>374101.6241107337</v>
+        <v>374101.6215427137</v>
       </c>
       <c r="C8">
         <v>253807.7277</v>
       </c>
       <c r="D8">
-        <v>120293.8964107338</v>
+        <v>120293.8938427137</v>
       </c>
       <c r="E8">
-        <v>1.473956792020615</v>
+        <v>1.473956781902641</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -643,16 +643,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>27013.28356984481</v>
+        <v>27013.28319965587</v>
       </c>
       <c r="C10">
         <v>73558.118705595</v>
       </c>
       <c r="D10">
-        <v>-46544.8351357502</v>
+        <v>-46544.83550593913</v>
       </c>
       <c r="E10">
-        <v>0.3672372818282819</v>
+        <v>0.3672372767956772</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -711,16 +711,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>232225.8431097768</v>
+        <v>232225.8420785568</v>
       </c>
       <c r="C14">
         <v>138127.9091</v>
       </c>
       <c r="D14">
-        <v>94097.9340097768</v>
+        <v>94097.93297855681</v>
       </c>
       <c r="E14">
-        <v>1.681237663140568</v>
+        <v>1.681237655674879</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -728,16 +728,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>113706.4305803962</v>
+        <v>113706.4272244541</v>
       </c>
       <c r="C15">
         <v>124993.859</v>
       </c>
       <c r="D15">
-        <v>-11287.42841960376</v>
+        <v>-11287.43177554589</v>
       </c>
       <c r="E15">
-        <v>0.9096961361949489</v>
+        <v>0.9096961093460928</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -745,16 +745,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>7015.546929735239</v>
+        <v>7015.542250428573</v>
       </c>
       <c r="C16">
         <v>25315.8782</v>
       </c>
       <c r="D16">
-        <v>-18300.33127026476</v>
+        <v>-18300.33594957142</v>
       </c>
       <c r="E16">
-        <v>0.277120425146272</v>
+        <v>0.2771202403094423</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -847,16 +847,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>291924.3013799793</v>
+        <v>291924.2976924526</v>
       </c>
       <c r="C22">
         <v>294608.3971</v>
       </c>
       <c r="D22">
-        <v>-2684.095720020705</v>
+        <v>-2684.099407547386</v>
       </c>
       <c r="E22">
-        <v>0.990889276251316</v>
+        <v>0.9908892637346101</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -898,16 +898,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>14662.91350190787</v>
+        <v>14662.91319299709</v>
       </c>
       <c r="C25">
         <v>16417.766</v>
       </c>
       <c r="D25">
-        <v>-1754.85249809213</v>
+        <v>-1754.852807002908</v>
       </c>
       <c r="E25">
-        <v>0.8931125892467873</v>
+        <v>0.8931125704311471</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -966,16 +966,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>9150.177149098128</v>
+        <v>9150.176523101461</v>
       </c>
       <c r="C29">
         <v>14214.106</v>
       </c>
       <c r="D29">
-        <v>-5063.928850901872</v>
+        <v>-5063.929476898538</v>
       </c>
       <c r="E29">
-        <v>0.6437391946491836</v>
+        <v>0.6437391506086603</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -983,16 +983,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>28000.73411985165</v>
+        <v>28000.73376398499</v>
       </c>
       <c r="C30">
         <v>45467.19299</v>
       </c>
       <c r="D30">
-        <v>-17466.45887014835</v>
+        <v>-17466.45922601502</v>
       </c>
       <c r="E30">
-        <v>0.6158447944215535</v>
+        <v>0.6158447865946647</v>
       </c>
     </row>
     <row r="31" spans="1:5">

--- a/data/Quality control/ghg_comparison.xlsx
+++ b/data/Quality control/ghg_comparison.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Quality control/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_277D62F5F613C846451D04B52237D1EC7552D94D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689F54CA-6952-449E-A4A2-26C9E01546C8}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>tCO2eq_estimated</t>
   </si>
@@ -43,24 +52,12 @@
     <t>BC-MAIN-8eb8be0d</t>
   </si>
   <si>
-    <t>BC-MAIN-aa76f6f2</t>
-  </si>
-  <si>
-    <t>BC-MAIN-ed23117f</t>
-  </si>
-  <si>
     <t>GRP-0a2c0d69</t>
   </si>
   <si>
-    <t>GRP-0d911886</t>
-  </si>
-  <si>
     <t>GRP-147b3123</t>
   </si>
   <si>
-    <t>GRP-14bfbb82</t>
-  </si>
-  <si>
     <t>GRP-a13779f8</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>QC-MAIN-6dc537e6</t>
   </si>
   <si>
-    <t>QC-MAIN-9de9bb0d</t>
-  </si>
-  <si>
     <t>QC-MAIN-b86f7d07</t>
   </si>
   <si>
@@ -119,19 +113,13 @@
   </si>
   <si>
     <t>QC-MAIN-e7e6a960</t>
-  </si>
-  <si>
-    <t>QC-MAIN-f9e41c2a</t>
-  </si>
-  <si>
-    <t>YT-MAIN-44857446</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,12 +136,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -183,24 +177,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -238,7 +244,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -272,6 +278,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -306,9 +313,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -481,11 +489,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -502,24 +517,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>6283.1679065491</v>
-      </c>
-      <c r="C2">
-        <v>70401.57769000001</v>
-      </c>
-      <c r="D2">
-        <v>-64118.40978345091</v>
-      </c>
-      <c r="E2">
-        <v>0.08924754405669484</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="B2" s="3">
+        <v>6283.1679065490998</v>
+      </c>
+      <c r="C2" s="3">
+        <v>70401.577690000006</v>
+      </c>
+      <c r="D2" s="3">
+        <v>-64118.409783450908</v>
+      </c>
+      <c r="E2" s="3">
+        <v>8.9247544056694841E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -533,520 +548,406 @@
         <v>-9515.726484563449</v>
       </c>
       <c r="E3">
-        <v>0.9265267965369675</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.92652679653696746</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>40875.43207764778</v>
+        <v>40875.432077647783</v>
       </c>
       <c r="C4">
-        <v>27335.62395</v>
+        <v>27335.623950000001</v>
       </c>
       <c r="D4">
-        <v>13539.80812764778</v>
+        <v>13539.808127647781</v>
       </c>
       <c r="E4">
         <v>1.495317324836398</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>102581.6441920313</v>
+        <v>102581.64419203129</v>
       </c>
       <c r="C5">
-        <v>95697.6225</v>
+        <v>95697.622499999998</v>
       </c>
       <c r="D5">
         <v>6884.021692031296</v>
       </c>
       <c r="E5">
-        <v>1.071935138117264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.0719351381172639</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>23612.4993404836</v>
+        <v>374101.62154271372</v>
       </c>
       <c r="C6">
-        <v>15908.3</v>
+        <v>253807.72769999999</v>
       </c>
       <c r="D6">
-        <v>7704.199340483596</v>
+        <v>120293.8938427137</v>
       </c>
       <c r="E6">
-        <v>1.484288034578402</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.4739567819026409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>74891.21331786228</v>
+        <v>27013.283199655871</v>
       </c>
       <c r="C7">
-        <v>72492</v>
+        <v>37940.749479999999</v>
       </c>
       <c r="D7">
-        <v>2399.213317862275</v>
+        <v>-10927.46628034413</v>
       </c>
       <c r="E7">
-        <v>1.033096249487699</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>0.71198601951433749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>374101.6215427137</v>
+        <v>30049.933466104401</v>
       </c>
       <c r="C8">
-        <v>253807.7277</v>
+        <v>23304.800200000001</v>
       </c>
       <c r="D8">
-        <v>120293.8938427137</v>
+        <v>6745.1332661043962</v>
       </c>
       <c r="E8">
-        <v>1.473956781902641</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>1.289431070346803</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>63357.17475788935</v>
+        <v>146455.53884009109</v>
       </c>
       <c r="C9">
-        <v>57797.1544138831</v>
+        <v>110503.4497</v>
       </c>
       <c r="D9">
-        <v>5560.020344006247</v>
+        <v>35952.089140091062</v>
       </c>
       <c r="E9">
-        <v>1.096198859621897</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
+        <v>1.325348115716708</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10">
-        <v>27013.28319965587</v>
-      </c>
-      <c r="C10">
-        <v>73558.118705595</v>
-      </c>
-      <c r="D10">
-        <v>-46544.83550593913</v>
-      </c>
-      <c r="E10">
-        <v>0.3672372767956772</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="B10" s="3">
+        <v>232225.8420785568</v>
+      </c>
+      <c r="C10" s="3">
+        <v>138127.90909999999</v>
+      </c>
+      <c r="D10" s="3">
+        <v>94097.932978556812</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1.6812376556748789</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>11954.40315924068</v>
+        <v>113706.42722445411</v>
       </c>
       <c r="C11">
-        <v>14002</v>
+        <v>124993.859</v>
       </c>
       <c r="D11">
-        <v>-2047.596840759317</v>
+        <v>-11287.431775545891</v>
       </c>
       <c r="E11">
-        <v>0.8537639736638111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="1" t="s">
+        <v>0.9096961093460928</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
-        <v>30049.9334661044</v>
-      </c>
-      <c r="C12">
-        <v>23332.8002</v>
-      </c>
-      <c r="D12">
-        <v>6717.133266104396</v>
-      </c>
-      <c r="E12">
-        <v>1.28788371770759</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="B12" s="3">
+        <v>7015.5422504285734</v>
+      </c>
+      <c r="C12" s="3">
+        <v>25315.878199999999</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-18300.335949571421</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.27712024030944232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>146455.5388400911</v>
+        <v>20238.81830973483</v>
       </c>
       <c r="C13">
-        <v>110503.4497</v>
+        <v>20107.965</v>
       </c>
       <c r="D13">
-        <v>35952.08914009106</v>
+        <v>130.8533097348263</v>
       </c>
       <c r="E13">
-        <v>1.325348115716708</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="1" t="s">
+        <v>1.0065075361795599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14">
-        <v>232225.8420785568</v>
-      </c>
-      <c r="C14">
-        <v>138127.9091</v>
-      </c>
-      <c r="D14">
-        <v>94097.93297855681</v>
-      </c>
-      <c r="E14">
-        <v>1.681237655674879</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="1" t="s">
+      <c r="B14" s="3">
+        <v>124842.74883</v>
+      </c>
+      <c r="C14" s="3">
+        <v>19248.270400000001</v>
+      </c>
+      <c r="D14" s="3">
+        <v>105594.47843</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.4859203572909072</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>113706.4272244541</v>
-      </c>
-      <c r="C15">
-        <v>124993.859</v>
-      </c>
-      <c r="D15">
-        <v>-11287.43177554589</v>
-      </c>
-      <c r="E15">
-        <v>0.9096961093460928</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="1" t="s">
+      <c r="B15" s="3">
+        <v>10558.860176517979</v>
+      </c>
+      <c r="C15" s="3">
+        <v>21634.757000000001</v>
+      </c>
+      <c r="D15" s="3">
+        <v>-11075.89682348202</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.48805078682039171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>7015.542250428573</v>
-      </c>
-      <c r="C16">
-        <v>25315.8782</v>
-      </c>
-      <c r="D16">
-        <v>-18300.33594957142</v>
-      </c>
-      <c r="E16">
-        <v>0.2771202403094423</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="B16" s="3">
+        <v>9108.190113087674</v>
+      </c>
+      <c r="C16" s="3">
+        <v>26796.345969999998</v>
+      </c>
+      <c r="D16" s="3">
+        <v>-17688.155856912319</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.33990418407363449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>20238.81830973483</v>
+        <v>35578.001059861519</v>
       </c>
       <c r="C17">
-        <v>20107.965</v>
+        <v>56107.381999999998</v>
       </c>
       <c r="D17">
-        <v>130.8533097348263</v>
+        <v>-20529.380940138479</v>
       </c>
       <c r="E17">
-        <v>1.00650753617956</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>0.63410552750191629</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>124842.74883</v>
+        <v>291924.29769245262</v>
       </c>
       <c r="C18">
-        <v>19248.2704</v>
+        <v>294608.3971</v>
       </c>
       <c r="D18">
-        <v>105594.47843</v>
+        <v>-2684.0994075473859</v>
       </c>
       <c r="E18">
-        <v>6.485920357290907</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1" t="s">
+        <v>0.99088926373461006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19">
-        <v>10558.86017651798</v>
-      </c>
-      <c r="C19">
-        <v>21634.757</v>
-      </c>
-      <c r="D19">
-        <v>-11075.89682348202</v>
-      </c>
-      <c r="E19">
-        <v>0.4880507868203917</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="B19" s="3">
+        <v>36251.555083860068</v>
+      </c>
+      <c r="C19" s="3">
+        <v>12403.638000000001</v>
+      </c>
+      <c r="D19" s="3">
+        <v>23847.917083860069</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.9226550374865878</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B20">
-        <v>9108.190113087674</v>
+        <v>36676.523886086383</v>
       </c>
       <c r="C20">
-        <v>26796.34597</v>
+        <v>36874.774010000001</v>
       </c>
       <c r="D20">
-        <v>-17688.15585691232</v>
+        <v>-198.2501239136254</v>
       </c>
       <c r="E20">
-        <v>0.3399041840736345</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.99462369250426153</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B21">
-        <v>35578.00105986152</v>
+        <v>14662.91319299709</v>
       </c>
       <c r="C21">
-        <v>56107.382</v>
+        <v>16417.766</v>
       </c>
       <c r="D21">
-        <v>-20529.38094013848</v>
+        <v>-1754.8528070029081</v>
       </c>
       <c r="E21">
-        <v>0.6341055275019163</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>0.89311257043114711</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B22">
-        <v>291924.2976924526</v>
+        <v>36931.116935558202</v>
       </c>
       <c r="C22">
-        <v>294608.3971</v>
+        <v>37245.561999999998</v>
       </c>
       <c r="D22">
-        <v>-2684.099407547386</v>
+        <v>-314.44506444180303</v>
       </c>
       <c r="E22">
-        <v>0.9908892637346101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.99155751591446506</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B23">
-        <v>36251.55508386007</v>
+        <v>30198.711343158309</v>
       </c>
       <c r="C23">
-        <v>12403.638</v>
+        <v>33407.658000000003</v>
       </c>
       <c r="D23">
-        <v>23847.91708386007</v>
+        <v>-3208.9466568416901</v>
       </c>
       <c r="E23">
-        <v>2.922655037486588</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>0.90394577623963679</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>36676.52388608638</v>
+        <v>9150.1765231014615</v>
       </c>
       <c r="C24">
-        <v>36874.77401</v>
+        <v>14214.106</v>
       </c>
       <c r="D24">
-        <v>-198.2501239136254</v>
+        <v>-5063.9294768985383</v>
       </c>
       <c r="E24">
-        <v>0.9946236925042615</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>0.64373915060866027</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <v>14662.91319299709</v>
+        <v>28000.73376398499</v>
       </c>
       <c r="C25">
-        <v>16417.766</v>
+        <v>45467.192990000003</v>
       </c>
       <c r="D25">
-        <v>-1754.852807002908</v>
+        <v>-17466.45922601502</v>
       </c>
       <c r="E25">
-        <v>0.8931125704311471</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>0.61584478659466468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B26">
-        <v>36931.1169355582</v>
+        <v>181786.2801864825</v>
       </c>
       <c r="C26">
-        <v>37245.562</v>
+        <v>195814.68040000001</v>
       </c>
       <c r="D26">
-        <v>-314.445064441803</v>
+        <v>-14028.400213517511</v>
       </c>
       <c r="E26">
-        <v>0.9915575159144651</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27">
-        <v>10809.1719204319</v>
-      </c>
-      <c r="C27">
-        <v>4109</v>
-      </c>
-      <c r="D27">
-        <v>6700.171920431903</v>
-      </c>
-      <c r="E27">
-        <v>2.630608887912364</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28">
-        <v>30198.71134315831</v>
-      </c>
-      <c r="C28">
-        <v>33407.658</v>
-      </c>
-      <c r="D28">
-        <v>-3208.94665684169</v>
-      </c>
-      <c r="E28">
-        <v>0.9039457762396368</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29">
-        <v>9150.176523101461</v>
-      </c>
-      <c r="C29">
-        <v>14214.106</v>
-      </c>
-      <c r="D29">
-        <v>-5063.929476898538</v>
-      </c>
-      <c r="E29">
-        <v>0.6437391506086603</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30">
-        <v>28000.73376398499</v>
-      </c>
-      <c r="C30">
-        <v>45467.19299</v>
-      </c>
-      <c r="D30">
-        <v>-17466.45922601502</v>
-      </c>
-      <c r="E30">
-        <v>0.6158447865946647</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31">
-        <v>181786.2801864825</v>
-      </c>
-      <c r="C31">
-        <v>195814.6804</v>
-      </c>
-      <c r="D31">
-        <v>-14028.40021351751</v>
-      </c>
-      <c r="E31">
-        <v>0.9283587921760461</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32">
-        <v>13637.62339983279</v>
-      </c>
-      <c r="C32">
-        <v>18188</v>
-      </c>
-      <c r="D32">
-        <v>-4550.376600167214</v>
-      </c>
-      <c r="E32">
-        <v>0.7498143501117652</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33">
-        <v>6679.33873725765</v>
-      </c>
-      <c r="C33">
-        <v>7271</v>
-      </c>
-      <c r="D33">
-        <v>-591.6612627423501</v>
-      </c>
-      <c r="E33">
-        <v>0.9186272503448838</v>
+        <v>0.92835879217604611</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E26">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Quality control/ghg_comparison.xlsx
+++ b/data/Quality control/ghg_comparison.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Quality control/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_277D62F5F613C846451D04B52237D1EC7552D94D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689F54CA-6952-449E-A4A2-26C9E01546C8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>tCO2eq_estimated</t>
   </si>
@@ -52,12 +43,24 @@
     <t>BC-MAIN-8eb8be0d</t>
   </si>
   <si>
+    <t>BC-MAIN-aa76f6f2</t>
+  </si>
+  <si>
+    <t>BC-MAIN-ed23117f</t>
+  </si>
+  <si>
     <t>GRP-0a2c0d69</t>
   </si>
   <si>
+    <t>GRP-0d911886</t>
+  </si>
+  <si>
     <t>GRP-147b3123</t>
   </si>
   <si>
+    <t>GRP-14bfbb82</t>
+  </si>
+  <si>
     <t>GRP-a13779f8</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>QC-MAIN-6dc537e6</t>
   </si>
   <si>
+    <t>QC-MAIN-9de9bb0d</t>
+  </si>
+  <si>
     <t>QC-MAIN-b86f7d07</t>
   </si>
   <si>
@@ -113,13 +119,19 @@
   </si>
   <si>
     <t>QC-MAIN-e7e6a960</t>
+  </si>
+  <si>
+    <t>QC-MAIN-f9e41c2a</t>
+  </si>
+  <si>
+    <t>YT-MAIN-44857446</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,18 +148,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -177,36 +183,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -244,7 +238,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -278,7 +272,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -313,10 +306,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,18 +481,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -517,24 +502,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
-        <v>6283.1679065490998</v>
-      </c>
-      <c r="C2" s="3">
-        <v>70401.577690000006</v>
-      </c>
-      <c r="D2" s="3">
-        <v>-64118.409783450908</v>
-      </c>
-      <c r="E2" s="3">
-        <v>8.9247544056694841E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>6283.1679065491</v>
+      </c>
+      <c r="C2">
+        <v>70401.57769000001</v>
+      </c>
+      <c r="D2">
+        <v>-64118.40978345091</v>
+      </c>
+      <c r="E2">
+        <v>0.08924754405669484</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -548,406 +533,520 @@
         <v>-9515.726484563449</v>
       </c>
       <c r="E3">
-        <v>0.92652679653696746</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.9265267965369675</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>40875.432077647783</v>
+        <v>40875.43207764778</v>
       </c>
       <c r="C4">
-        <v>27335.623950000001</v>
+        <v>27335.62395</v>
       </c>
       <c r="D4">
-        <v>13539.808127647781</v>
+        <v>13539.80812764778</v>
       </c>
       <c r="E4">
         <v>1.495317324836398</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>102581.64419203129</v>
+        <v>102581.6441920313</v>
       </c>
       <c r="C5">
-        <v>95697.622499999998</v>
+        <v>95697.6225</v>
       </c>
       <c r="D5">
         <v>6884.021692031296</v>
       </c>
       <c r="E5">
-        <v>1.0719351381172639</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.071935138117264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>374101.62154271372</v>
+        <v>23612.4993404836</v>
       </c>
       <c r="C6">
-        <v>253807.72769999999</v>
+        <v>15908.3</v>
       </c>
       <c r="D6">
-        <v>120293.8938427137</v>
+        <v>7704.199340483596</v>
       </c>
       <c r="E6">
-        <v>1.4739567819026409</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.484288034578402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>27013.283199655871</v>
+        <v>74891.21331786228</v>
       </c>
       <c r="C7">
-        <v>37940.749479999999</v>
+        <v>72492</v>
       </c>
       <c r="D7">
-        <v>-10927.46628034413</v>
+        <v>2399.213317862275</v>
       </c>
       <c r="E7">
-        <v>0.71198601951433749</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.033096249487699</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>30049.933466104401</v>
+        <v>374101.6215427137</v>
       </c>
       <c r="C8">
-        <v>23304.800200000001</v>
+        <v>253807.7277</v>
       </c>
       <c r="D8">
-        <v>6745.1332661043962</v>
+        <v>120293.8938427137</v>
       </c>
       <c r="E8">
-        <v>1.289431070346803</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.473956781902641</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9">
-        <v>146455.53884009109</v>
+        <v>63357.17475788935</v>
       </c>
       <c r="C9">
-        <v>110503.4497</v>
+        <v>115594.3088277662</v>
       </c>
       <c r="D9">
-        <v>35952.089140091062</v>
+        <v>-52237.13406987685</v>
       </c>
       <c r="E9">
-        <v>1.325348115716708</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+        <v>0.5480994298109485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3">
-        <v>232225.8420785568</v>
-      </c>
-      <c r="C10" s="3">
-        <v>138127.90909999999</v>
-      </c>
-      <c r="D10" s="3">
-        <v>94097.932978556812</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1.6812376556748789</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>27013.28319965587</v>
+      </c>
+      <c r="C10">
+        <v>109175.48793119</v>
+      </c>
+      <c r="D10">
+        <v>-82162.20473153413</v>
+      </c>
+      <c r="E10">
+        <v>0.2474299287462908</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11">
-        <v>113706.42722445411</v>
+        <v>11954.40315924068</v>
       </c>
       <c r="C11">
-        <v>124993.859</v>
+        <v>28004</v>
       </c>
       <c r="D11">
-        <v>-11287.431775545891</v>
+        <v>-16049.59684075932</v>
       </c>
       <c r="E11">
-        <v>0.9096961093460928</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+        <v>0.4268819868319055</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3">
-        <v>7015.5422504285734</v>
-      </c>
-      <c r="C12" s="3">
-        <v>25315.878199999999</v>
-      </c>
-      <c r="D12" s="3">
-        <v>-18300.335949571421</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0.27712024030944232</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>30049.9334661044</v>
+      </c>
+      <c r="C12">
+        <v>23360.8002</v>
+      </c>
+      <c r="D12">
+        <v>6689.133266104396</v>
+      </c>
+      <c r="E12">
+        <v>1.286340074348326</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>20238.81830973483</v>
+        <v>146455.5388400911</v>
       </c>
       <c r="C13">
-        <v>20107.965</v>
+        <v>110503.4497</v>
       </c>
       <c r="D13">
-        <v>130.8533097348263</v>
+        <v>35952.08914009106</v>
       </c>
       <c r="E13">
-        <v>1.0065075361795599</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+        <v>1.325348115716708</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3">
-        <v>124842.74883</v>
-      </c>
-      <c r="C14" s="3">
-        <v>19248.270400000001</v>
-      </c>
-      <c r="D14" s="3">
-        <v>105594.47843</v>
-      </c>
-      <c r="E14" s="3">
-        <v>6.4859203572909072</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B14">
+        <v>232225.8420785568</v>
+      </c>
+      <c r="C14">
+        <v>138127.9091</v>
+      </c>
+      <c r="D14">
+        <v>94097.93297855681</v>
+      </c>
+      <c r="E14">
+        <v>1.681237655674879</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3">
-        <v>10558.860176517979</v>
-      </c>
-      <c r="C15" s="3">
-        <v>21634.757000000001</v>
-      </c>
-      <c r="D15" s="3">
-        <v>-11075.89682348202</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.48805078682039171</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B15">
+        <v>113706.4272244541</v>
+      </c>
+      <c r="C15">
+        <v>124993.859</v>
+      </c>
+      <c r="D15">
+        <v>-11287.43177554589</v>
+      </c>
+      <c r="E15">
+        <v>0.9096961093460928</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="3">
-        <v>9108.190113087674</v>
-      </c>
-      <c r="C16" s="3">
-        <v>26796.345969999998</v>
-      </c>
-      <c r="D16" s="3">
-        <v>-17688.155856912319</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0.33990418407363449</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>7015.542250428573</v>
+      </c>
+      <c r="C16">
+        <v>25315.8782</v>
+      </c>
+      <c r="D16">
+        <v>-18300.33594957142</v>
+      </c>
+      <c r="E16">
+        <v>0.2771202403094423</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B17">
-        <v>35578.001059861519</v>
+        <v>20238.81830973483</v>
       </c>
       <c r="C17">
-        <v>56107.381999999998</v>
+        <v>20107.965</v>
       </c>
       <c r="D17">
-        <v>-20529.380940138479</v>
+        <v>130.8533097348263</v>
       </c>
       <c r="E17">
-        <v>0.63410552750191629</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.00650753617956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B18">
-        <v>291924.29769245262</v>
+        <v>124842.74883</v>
       </c>
       <c r="C18">
-        <v>294608.3971</v>
+        <v>19248.2704</v>
       </c>
       <c r="D18">
-        <v>-2684.0994075473859</v>
+        <v>105594.47843</v>
       </c>
       <c r="E18">
-        <v>0.99088926373461006</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+        <v>6.485920357290907</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3">
-        <v>36251.555083860068</v>
-      </c>
-      <c r="C19" s="3">
-        <v>12403.638000000001</v>
-      </c>
-      <c r="D19" s="3">
-        <v>23847.917083860069</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2.9226550374865878</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>10558.86017651798</v>
+      </c>
+      <c r="C19">
+        <v>21634.757</v>
+      </c>
+      <c r="D19">
+        <v>-11075.89682348202</v>
+      </c>
+      <c r="E19">
+        <v>0.4880507868203917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B20">
-        <v>36676.523886086383</v>
+        <v>9108.190113087674</v>
       </c>
       <c r="C20">
-        <v>36874.774010000001</v>
+        <v>26796.34597</v>
       </c>
       <c r="D20">
-        <v>-198.2501239136254</v>
+        <v>-17688.15585691232</v>
       </c>
       <c r="E20">
-        <v>0.99462369250426153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.3399041840736345</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B21">
-        <v>14662.91319299709</v>
+        <v>35578.00105986152</v>
       </c>
       <c r="C21">
-        <v>16417.766</v>
+        <v>56107.382</v>
       </c>
       <c r="D21">
-        <v>-1754.8528070029081</v>
+        <v>-20529.38094013848</v>
       </c>
       <c r="E21">
-        <v>0.89311257043114711</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.6341055275019163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B22">
-        <v>36931.116935558202</v>
+        <v>291924.2976924526</v>
       </c>
       <c r="C22">
-        <v>37245.561999999998</v>
+        <v>294608.3971</v>
       </c>
       <c r="D22">
-        <v>-314.44506444180303</v>
+        <v>-2684.099407547386</v>
       </c>
       <c r="E22">
-        <v>0.99155751591446506</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.9908892637346101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B23">
-        <v>30198.711343158309</v>
+        <v>36251.55508386007</v>
       </c>
       <c r="C23">
-        <v>33407.658000000003</v>
+        <v>12403.638</v>
       </c>
       <c r="D23">
-        <v>-3208.9466568416901</v>
+        <v>23847.91708386007</v>
       </c>
       <c r="E23">
-        <v>0.90394577623963679</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.922655037486588</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>9150.1765231014615</v>
+        <v>36676.52388608638</v>
       </c>
       <c r="C24">
-        <v>14214.106</v>
+        <v>36874.77401</v>
       </c>
       <c r="D24">
-        <v>-5063.9294768985383</v>
+        <v>-198.2501239136254</v>
       </c>
       <c r="E24">
-        <v>0.64373915060866027</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.9946236925042615</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <v>28000.73376398499</v>
+        <v>14662.91319299709</v>
       </c>
       <c r="C25">
-        <v>45467.192990000003</v>
+        <v>16417.766</v>
       </c>
       <c r="D25">
-        <v>-17466.45922601502</v>
+        <v>-1754.852807002908</v>
       </c>
       <c r="E25">
-        <v>0.61584478659466468</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.8931125704311471</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B26">
+        <v>36931.1169355582</v>
+      </c>
+      <c r="C26">
+        <v>37245.562</v>
+      </c>
+      <c r="D26">
+        <v>-314.445064441803</v>
+      </c>
+      <c r="E26">
+        <v>0.9915575159144651</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
+        <v>10809.1719204319</v>
+      </c>
+      <c r="C27">
+        <v>4109</v>
+      </c>
+      <c r="D27">
+        <v>6700.171920431903</v>
+      </c>
+      <c r="E27">
+        <v>2.630608887912364</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
+        <v>30198.71134315831</v>
+      </c>
+      <c r="C28">
+        <v>33407.658</v>
+      </c>
+      <c r="D28">
+        <v>-3208.94665684169</v>
+      </c>
+      <c r="E28">
+        <v>0.9039457762396368</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>9150.176523101461</v>
+      </c>
+      <c r="C29">
+        <v>14214.106</v>
+      </c>
+      <c r="D29">
+        <v>-5063.929476898538</v>
+      </c>
+      <c r="E29">
+        <v>0.6437391506086603</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30">
+        <v>28000.73376398499</v>
+      </c>
+      <c r="C30">
+        <v>45467.19299</v>
+      </c>
+      <c r="D30">
+        <v>-17466.45922601502</v>
+      </c>
+      <c r="E30">
+        <v>0.6158447865946647</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31">
         <v>181786.2801864825</v>
       </c>
-      <c r="C26">
-        <v>195814.68040000001</v>
-      </c>
-      <c r="D26">
-        <v>-14028.400213517511</v>
-      </c>
-      <c r="E26">
-        <v>0.92835879217604611</v>
+      <c r="C31">
+        <v>195814.6804</v>
+      </c>
+      <c r="D31">
+        <v>-14028.40021351751</v>
+      </c>
+      <c r="E31">
+        <v>0.9283587921760461</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32">
+        <v>13637.62339983279</v>
+      </c>
+      <c r="C32">
+        <v>18188</v>
+      </c>
+      <c r="D32">
+        <v>-4550.376600167214</v>
+      </c>
+      <c r="E32">
+        <v>0.7498143501117652</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>6679.33873725765</v>
+      </c>
+      <c r="C33">
+        <v>7271</v>
+      </c>
+      <c r="D33">
+        <v>-591.6612627423501</v>
+      </c>
+      <c r="E33">
+        <v>0.9186272503448838</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E26">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>